--- a/stories/arbres/ATOM-AUT.RAN.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Constantin joue dans le salon. Les cubes sont partout. Papa dit : on range. Les jouets retournent dans la caisse. Constantin prend un cube. Il le met dans la caisse. Il prend une voiture. Il la met dans la caisse. Papa aide. Ils rangent ensemble. La caisse se remplit. Le tapis redevient vide. Constantin dit : j'ai rangé. Papa sourit. Constantin pousse la caisse. La caisse va près du meuble. Ranger, c'est mettre dans la caisse. Papa dit : merci. Constantin tape des mains.</t>
+          <t>Constantin joue dans le salon. Les cubes sont partout. On range. Les jouets retournent dans la caisse. Constantin prend un cube. Il le met dans la caisse. Il prend une voiture. Il la met dans la caisse. Papa aide. Ils rangent ensemble. La caisse se remplit. Le tapis redevient vide. J'ai rangé. Papa sourit. Constantin pousse la caisse. La caisse va près du meuble. Ranger, c'est mettre dans la caisse. Merci. Constantin tape des mains.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Constantin joue dans le salon. Les cubes sont partout.
+papa|On range.
+narrateur|Les jouets retournent dans la caisse. Constantin prend un cube. Il le met dans la caisse. Il prend une voiture. Il la met dans la caisse. Papa aide. Ils rangent ensemble. La caisse se remplit. Le tapis redevient vide.
+enfant-m|J'ai rangé. Papa sourit.
+narrateur|Constantin pousse la caisse. La caisse va près du meuble. Ranger, c'est mettre dans la caisse.
+papa|Merci.
+narrateur|Constantin tape des mains.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le jeu est fini. Que fait Constantin ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Constantin a rangé. Les cubes sont dans la caisse. Papa a aidé.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Constantin s'assoit près de papa. Le salon est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.RAN.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Constantin tape des mains.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Le jeu est fini. Que fait Constantin ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1681,7 @@
           <t>narrateur|Constantin a rangé. Les cubes sont dans la caisse. Papa a aidé.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1845,7 @@
           <t>narrateur|Constantin s'assoit près de papa. Le salon est calme.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-AUT.RAN.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Constantin range dans la caisse</t>
+          <t>Les cubes près du radiateur</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Près du radiateur, Mila pose des cubes. Quand le jeu s'arrête, les cubes rentrent dans la caisse.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Constantin joue dans le salon. Les cubes sont partout. On range. Les jouets retournent dans la caisse. Constantin prend un cube. Il le met dans la caisse. Il prend une voiture. Il la met dans la caisse. Papa aide. Ils rangent ensemble. La caisse se remplit. Le tapis redevient vide. J'ai rangé. Papa sourit. Constantin pousse la caisse. La caisse va près du meuble. Ranger, c'est mettre dans la caisse. Merci. Constantin tape des mains.</t>
+          <t>Le radiateur est tout chaud. Des chaussettes de laine attendent près du canapé. Elles sont épaisses. Elles sentent le linge propre. Les chaussettes sont chaudes, papa. Oui. On les laisse près du radiateur. Une caisse en bois est au salon. Elle sent la forêt. Mila, en ce moment, est près du canapé. Elle touche un cube. Le cube est lisse. Il est chaud, papa. C'est le radiateur, Mila. Mila pose un cube. Puis un autre cube. Clic. Elle fait une petite tour. Ta tour est jolie. Elle est petite, maman. Mila pose encore un cube. Clic. Puis le jeu est fini. On range. Les jouets retournent dans la caisse. Mila prend un cube. Elle le met dans la caisse. Toc. Elle prend une petite voiture. Elle la met dans la caisse. Toc. On range ensemble. Papa aide. Ils rangent ensemble. La caisse se remplit. Le tapis redevient vide. J'ai rangé. Bravo, Mila. Ranger, c'est mettre dans la caisse. Mila pousse la caisse. La caisse va près du meuble. Tu as fini de ranger tes jouets ? Oui, papa. Merci. Tu as fait du bon travail. Mila tape des mains.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,20 +1324,54 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Constantin joue dans le salon. Les cubes sont partout.
+          <t>narrateur|Le radiateur est tout chaud.
+narrateur|Des chaussettes de laine attendent près du canapé.
+narrateur|Elles sont épaisses.
+narrateur|Elles sentent le linge propre.
+maman|Les chaussettes sont chaudes, papa.
+papa|Oui. On les laisse près du radiateur.
+narrateur|Une caisse en bois est au salon.
+narrateur|Elle sent la forêt.
+narrateur|Mila, en ce moment, est près du canapé.
+narrateur|Elle touche un cube.
+narrateur|Le cube est lisse.
+enfant-f|Il est chaud, papa.
+papa|C'est le radiateur, Mila.
+narrateur|Mila pose un cube.
+narrateur|Puis un autre cube.
+narrateur|Clic.
+narrateur|Elle fait une petite tour.
+maman|Ta tour est jolie.
+enfant-f|Elle est petite, maman.
+narrateur|Mila pose encore un cube.
+narrateur|Clic.
+narrateur|Puis le jeu est fini.
 papa|On range.
-narrateur|Les jouets retournent dans la caisse. Constantin prend un cube. Il le met dans la caisse. Il prend une voiture. Il la met dans la caisse. Papa aide. Ils rangent ensemble. La caisse se remplit. Le tapis redevient vide.
-enfant-m|J'ai rangé. Papa sourit.
-narrateur|Constantin pousse la caisse. La caisse va près du meuble. Ranger, c'est mettre dans la caisse.
-papa|Merci.
-narrateur|Constantin tape des mains.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>voiture_passe</t>
-        </is>
-      </c>
+papa|Les jouets retournent dans la caisse.
+narrateur|Mila prend un cube.
+narrateur|Elle le met dans la caisse.
+narrateur|Toc.
+narrateur|Elle prend une petite voiture.
+narrateur|Elle la met dans la caisse.
+narrateur|Toc.
+papa|On range ensemble.
+narrateur|Papa aide.
+narrateur|Ils rangent ensemble.
+narrateur|La caisse se remplit.
+narrateur|Le tapis redevient vide.
+enfant-f|J'ai rangé.
+papa|Bravo, Mila.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Mila pousse la caisse.
+narrateur|La caisse va près du meuble.
+papa|Tu as fini de ranger tes jouets ?
+enfant-f|Oui, papa.
+maman|Merci.
+maman|Tu as fait du bon travail.
+narrateur|Mila tape des mains.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1350,7 +1396,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le jeu est fini. Que fait Constantin ?</t>
+          <t>Le jeu est fini. Que fait Mila ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1552,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le jeu est fini. Que fait Constantin ?</t>
+          <t>narrateur|Le jeu est fini. Que fait Mila ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1580,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Constantin a rangé. Les cubes sont dans la caisse. Papa a aidé.</t>
+          <t>Mila a rangé. Les cubes sont dans la caisse. Papa a aidé. On a rangé ensemble. Dans la caisse. Oui. Ranger, c'est mettre dans la caisse. Tu as fini de ranger tes jouets ? Oui. Bravo, Mila. C'est du bon travail. Le tapis est libre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1724,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Constantin a rangé. Les cubes sont dans la caisse. Papa a aidé.</t>
+          <t>narrateur|Mila a rangé.
+narrateur|Les cubes sont dans la caisse.
+narrateur|Papa a aidé.
+papa|On a rangé ensemble.
+enfant-f|Dans la caisse.
+maman|Oui. Ranger, c'est mettre dans la caisse.
+papa|Tu as fini de ranger tes jouets ?
+enfant-f|Oui.
+maman|Bravo, Mila.
+maman|C'est du bon travail.
+narrateur|Le tapis est libre.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1762,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Constantin s'assoit près de papa. Le salon est calme.</t>
+          <t>Mila s'assoit près de papa. Le salon est calme. Le radiateur chante un tout petit peu. Tu veux tes chaussettes chaudes ? Oui, maman. Maman lui tend les chaussettes. Elles sont douces. La caisse est à sa place. Les cubes dorment. Oui. Dans la caisse. On reste encore un peu ensemble ? Oui. Bravo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1898,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Constantin s'assoit près de papa. Le salon est calme.</t>
+          <t>narrateur|Mila s'assoit près de papa.
+narrateur|Le salon est calme.
+narrateur|Le radiateur chante un tout petit peu.
+maman|Tu veux tes chaussettes chaudes ?
+enfant-f|Oui, maman.
+narrateur|Maman lui tend les chaussettes.
+narrateur|Elles sont douces.
+papa|La caisse est à sa place.
+enfant-f|Les cubes dorment.
+papa|Oui. Dans la caisse.
+maman|On reste encore un peu ensemble ?
+enfant-f|Oui.
+papa|Bravo.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1938,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai mis les cubes dans la caisse. Bravo. Tu as fait du bon travail. Le radiateur reste chaud. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2078,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai mis les cubes dans la caisse.
+papa|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le radiateur reste chaud.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2142,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.RAN.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-06.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le radiateur est tout chaud. Des chaussettes de laine attendent près du canapé. Elles sont épaisses. Elles sentent le linge propre. Les chaussettes sont chaudes, papa. Oui. On les laisse près du radiateur. Une caisse en bois est au salon. Elle sent la forêt. Mila, en ce moment, est près du canapé. Elle touche un cube. Le cube est lisse. Il est chaud, papa. C'est le radiateur, Mila. Mila pose un cube. Puis un autre cube. Clic. Elle fait une petite tour. Ta tour est jolie. Elle est petite, maman. Mila pose encore un cube. Clic. Puis le jeu est fini. On range. Les jouets retournent dans la caisse. Mila prend un cube. Elle le met dans la caisse. Toc. Elle prend une petite voiture. Elle la met dans la caisse. Toc. On range ensemble. Papa aide. Ils rangent ensemble. La caisse se remplit. Le tapis redevient vide. J'ai rangé. Bravo, Mila. Ranger, c'est mettre dans la caisse. Mila pousse la caisse. La caisse va près du meuble. Tu as fini de ranger tes jouets ? Oui, papa. Merci. Tu as fait du bon travail. Mila tape des mains.</t>
+          <t>Le radiateur est tout chaud. Des chaussettes de laine attendent près du canapé. Elles sont épaisses. Elles sentent le linge propre. Les chaussettes sont chaudes, papa. Oui. On les laisse près du radiateur. Une caisse en bois est au salon. Elle sent la forêt. Mila, en ce moment, est près du canapé. Elle touche un cube. Le cube est lisse. Il est chaud, papa. C'est le radiateur, Mila. Mila pose un cube. Puis un autre cube. Clic. Elle fait une petite tour. Ta tour est jolie. Elle est petite, maman. Mila pose encore un cube. Clic. Ses pieds sont près du radiateur. Les orteils sont au chaud. Tu es bien, près du chaud. Oui, papa. C'est doux. Mila pose un cube rouge. La tour grandit un peu. Encore un cube, Mila ? Encore un cube. Clic. Puis le jeu est fini. On range. Les jouets retournent dans la caisse. Mila prend un cube. Elle le met dans la caisse. Toc. Elle prend une petite voiture. Elle la met dans la caisse. Toc. On range ensemble. Papa aide. Ils rangent ensemble. La caisse se remplit. Le tapis redevient vide. J'ai rangé. Bravo, Mila. Ranger, c'est mettre dans la caisse. Mila pousse la caisse. La caisse va près du meuble. Tu as fini de ranger tes jouets ? Oui, papa. Merci. Tu as fait du bon travail. Mila tape des mains. La caisse sent le bois, hein ? Oui. Le bois.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1344,6 +1344,15 @@
 maman|Ta tour est jolie.
 enfant-f|Elle est petite, maman.
 narrateur|Mila pose encore un cube.
+narrateur|Clic.
+narrateur|Ses pieds sont près du radiateur.
+narrateur|Les orteils sont au chaud.
+papa|Tu es bien, près du chaud.
+enfant-f|Oui, papa. C'est doux.
+narrateur|Mila pose un cube rouge.
+narrateur|La tour grandit un peu.
+maman|Encore un cube, Mila ?
+enfant-f|Encore un cube.
 narrateur|Clic.
 narrateur|Puis le jeu est fini.
 papa|On range.
@@ -1368,7 +1377,9 @@
 enfant-f|Oui, papa.
 maman|Merci.
 maman|Tu as fait du bon travail.
-narrateur|Mila tape des mains.</t>
+narrateur|Mila tape des mains.
+papa|La caisse sent le bois, hein ?
+enfant-f|Oui. Le bois.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1580,7 +1591,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a rangé. Les cubes sont dans la caisse. Papa a aidé. On a rangé ensemble. Dans la caisse. Oui. Ranger, c'est mettre dans la caisse. Tu as fini de ranger tes jouets ? Oui. Bravo, Mila. C'est du bon travail. Le tapis est libre.</t>
+          <t>Mila a rangé. Les cubes sont dans la caisse. Papa a aidé. On a rangé ensemble. Dans la caisse. Oui. Ranger, c'est mettre dans la caisse. Tu as fini de ranger tes jouets ? Oui. Bravo, Mila. C'est du bon travail. Le tapis est libre. Les pieds peuvent marcher, maintenant. Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1734,7 +1745,9 @@
 enfant-f|Oui.
 maman|Bravo, Mila.
 maman|C'est du bon travail.
-narrateur|Le tapis est libre.</t>
+narrateur|Le tapis est libre.
+papa|Les pieds peuvent marcher, maintenant.
+enfant-f|Oui, papa.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -2104,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2147,6 +2160,34 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-AUT.RAN.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-06.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Les cubes près du radiateur</t>
+          <t>Le livre du canapé</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Près du radiateur, Mila pose des cubes. Quand le jeu s'arrête, les cubes rentrent dans la caisse.</t>
+          <t>Mila veut le livre sur le canapé. Un cube est sur le coussin. Elle met les cubes dans la caisse. Le livre s'ouvre.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le radiateur est tout chaud. Des chaussettes de laine attendent près du canapé. Elles sont épaisses. Elles sentent le linge propre. Les chaussettes sont chaudes, papa. Oui. On les laisse près du radiateur. Une caisse en bois est au salon. Elle sent la forêt. Mila, en ce moment, est près du canapé. Elle touche un cube. Le cube est lisse. Il est chaud, papa. C'est le radiateur, Mila. Mila pose un cube. Puis un autre cube. Clic. Elle fait une petite tour. Ta tour est jolie. Elle est petite, maman. Mila pose encore un cube. Clic. Ses pieds sont près du radiateur. Les orteils sont au chaud. Tu es bien, près du chaud. Oui, papa. C'est doux. Mila pose un cube rouge. La tour grandit un peu. Encore un cube, Mila ? Encore un cube. Clic. Puis le jeu est fini. On range. Les jouets retournent dans la caisse. Mila prend un cube. Elle le met dans la caisse. Toc. Elle prend une petite voiture. Elle la met dans la caisse. Toc. On range ensemble. Papa aide. Ils rangent ensemble. La caisse se remplit. Le tapis redevient vide. J'ai rangé. Bravo, Mila. Ranger, c'est mettre dans la caisse. Mila pousse la caisse. La caisse va près du meuble. Tu as fini de ranger tes jouets ? Oui, papa. Merci. Tu as fait du bon travail. Mila tape des mains. La caisse sent le bois, hein ? Oui. Le bois.</t>
+          <t>La bouilloire chante tout doux. Pfff. La lampe fait un rond sur le canapé. Les mains de papa sentent le savon. L'eau est chaude, pour plus tard. Le livre est sur la table. Le livre a une couverture lisse. Un canard est dessus. Mila, en ce moment, est près du canapé. Elle touche un cube. Le cube est lisse. Je fais une petite tour. Une tour, avant le livre ? Oui. Une tour petite. Mila pose un cube. Puis un autre cube. Clic. Elle fait une petite tour. Ta tour est jolie. Elle est petite, papa. Mila pose un cube rouge. Clic. La tour grandit un peu. Elle touche le cube du haut. Le bois est tiède. Après, on lit le canard. Oui. Sur le canapé. Mila veut monter sur le canapé. Un cube est sur le coussin. Le livre ne peut pas s'ouvrir. Le livre fait une bosse. Un cube est sur le coussin. D'autres cubes sont au pied du canapé. Une petite voiture aussi. On n'a pas de place pour s'asseoir. Je voulais le canard. Le canard a besoin du coussin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Constantin joue dans le salon. Les cubes sont partout. Papa dit : on range. Les jouets retournent dans la caisse. Constantin prend un cube. Il le met dans la caisse. Il prend une voiture. Il la met dans la caisse. Papa aide. Ils rangent ensemble. La caisse se remplit. Le tapis redevient vide. Constantin dit : j'ai rangé. Papa sourit. Constantin pousse la caisse. La caisse va près du meuble. &lt;emphasis level="moderate"&gt;ranger&lt;/emphasis&gt;, c'est mettre dans la caisse. Papa dit : merci. Constantin tape des mains.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La bouilloire chante tout doux. Pfff. La lampe fait un rond sur le canapé. Les mains de papa sentent le savon. L'eau est chaude, pour plus tard. Le livre est sur la table. Le livre a une couverture lisse. Un canard est dessus. Mila, en ce moment, est près du canapé. Elle touche un cube. Le cube est lisse. Je fais une petite tour. Une tour, avant le livre ? Oui. Une tour petite. Mila pose un cube. Puis un autre cube. Clic. Elle fait une petite tour. Ta tour est jolie. Elle est petite, papa. Mila pose un cube rouge. Clic. La tour grandit un peu. Elle touche le cube du haut. Le bois est tiède. Après, on lit le canard. Oui. Sur le canapé. Mila veut monter sur le canapé. Un cube est sur le coussin. Le livre ne peut pas s'ouvrir. Le livre fait une bosse. Un cube est sur le coussin. D'autres cubes sont au pied du canapé. Une petite voiture aussi. On n'a pas de place pour s'asseoir. Je voulais le canard. Le canard a besoin du coussin.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1324,65 +1324,45 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le radiateur est tout chaud.
-narrateur|Des chaussettes de laine attendent près du canapé.
-narrateur|Elles sont épaisses.
-narrateur|Elles sentent le linge propre.
-maman|Les chaussettes sont chaudes, papa.
-papa|Oui. On les laisse près du radiateur.
-narrateur|Une caisse en bois est au salon.
-narrateur|Elle sent la forêt.
+          <t>narrateur|La bouilloire chante tout doux.
+narrateur|Pfff.
+narrateur|La lampe fait un rond sur le canapé.
+narrateur|Les mains de papa sentent le savon.
+maman|L'eau est chaude, pour plus tard.
+papa|Le livre est sur la table.
+narrateur|Le livre a une couverture lisse.
+narrateur|Un canard est dessus.
 narrateur|Mila, en ce moment, est près du canapé.
 narrateur|Elle touche un cube.
 narrateur|Le cube est lisse.
-enfant-f|Il est chaud, papa.
-papa|C'est le radiateur, Mila.
+enfant-f|Je fais une petite tour.
+maman|Une tour, avant le livre ?
+enfant-f|Oui. Une tour petite.
 narrateur|Mila pose un cube.
 narrateur|Puis un autre cube.
 narrateur|Clic.
 narrateur|Elle fait une petite tour.
-maman|Ta tour est jolie.
-enfant-f|Elle est petite, maman.
-narrateur|Mila pose encore un cube.
+papa|Ta tour est jolie.
+enfant-f|Elle est petite, papa.
+narrateur|Mila pose un cube rouge.
 narrateur|Clic.
-narrateur|Ses pieds sont près du radiateur.
-narrateur|Les orteils sont au chaud.
-papa|Tu es bien, près du chaud.
-enfant-f|Oui, papa. C'est doux.
-narrateur|Mila pose un cube rouge.
 narrateur|La tour grandit un peu.
-maman|Encore un cube, Mila ?
-enfant-f|Encore un cube.
-narrateur|Clic.
-narrateur|Puis le jeu est fini.
-papa|On range.
-papa|Les jouets retournent dans la caisse.
-narrateur|Mila prend un cube.
-narrateur|Elle le met dans la caisse.
-narrateur|Toc.
-narrateur|Elle prend une petite voiture.
-narrateur|Elle la met dans la caisse.
-narrateur|Toc.
-papa|On range ensemble.
-narrateur|Papa aide.
-narrateur|Ils rangent ensemble.
-narrateur|La caisse se remplit.
-narrateur|Le tapis redevient vide.
-enfant-f|J'ai rangé.
-papa|Bravo, Mila.
-maman|Ranger, c'est mettre dans la caisse.
-narrateur|Mila pousse la caisse.
-narrateur|La caisse va près du meuble.
-papa|Tu as fini de ranger tes jouets ?
-enfant-f|Oui, papa.
-maman|Merci.
-maman|Tu as fait du bon travail.
-narrateur|Mila tape des mains.
-papa|La caisse sent le bois, hein ?
-enfant-f|Oui. Le bois.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Elle touche le cube du haut.
+narrateur|Le bois est tiède.
+enfant-f|Après, on lit le canard.
+papa|Oui. Sur le canapé.
+narrateur|Mila veut monter sur le canapé.
+narrateur|Un cube est sur le coussin.
+narrateur|Le livre ne peut pas s'ouvrir.
+enfant-f|Le livre fait une bosse.
+maman|Un cube est sur le coussin.
+narrateur|D'autres cubes sont au pied du canapé.
+narrateur|Une petite voiture aussi.
+papa|On n'a pas de place pour s'asseoir.
+enfant-f|Je voulais le canard.
+maman|Le canard a besoin du coussin.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1412,7 +1392,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le jeu est fini. Que fait Constantin ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le jeu est fini. Que fait Mila ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1427,7 +1407,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>ranger | la caisse | dans la caisse</t>
+          <t>ranger | la caisse | dans la caisse | elle range</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1442,7 +1422,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Les jouets vont dans la caisse. Que fait-il ?</t>
+          <t>Elle met les cubes dans la caisse. Que fait Mila ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1566,7 +1546,6 @@
           <t>narrateur|Le jeu est fini. Que fait Mila ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1591,12 +1570,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a rangé. Les cubes sont dans la caisse. Papa a aidé. On a rangé ensemble. Dans la caisse. Oui. Ranger, c'est mettre dans la caisse. Tu as fini de ranger tes jouets ? Oui. Bravo, Mila. C'est du bon travail. Le tapis est libre. Les pieds peuvent marcher, maintenant. Oui, papa.</t>
+          <t>Mila prend le cube du coussin. La caisse est près du meuble. Elle met le cube dans la caisse. Toc. On va ranger. Tu ranges les cubes. Dans la caisse. Elle prend un cube au pied du canapé. Dans la caisse. Toc. Elle prend la petite voiture. Dans la caisse aussi. Le coussin est libre. Mila passe la main dessus. C'est mou. Le livre peut s'ouvrir. Oui. Plus de bosse.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Constantin a rangé. Les cubes sont dans la &lt;emphasis level="moderate"&gt;caisse&lt;/emphasis&gt;. Papa a aidé.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila prend le cube du coussin. La caisse est près du meuble. Elle met le cube dans la caisse. Toc. On va ranger. Tu ranges les cubes. Dans la caisse. Elle prend un cube au pied du canapé. Dans la caisse. Toc. Elle prend la petite voiture. Dans la caisse aussi. Le coussin est libre. Mila passe la main dessus. C'est mou. Le livre peut s'ouvrir. Oui. Plus de bosse.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1735,22 +1714,25 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Mila a rangé.
-narrateur|Les cubes sont dans la caisse.
-narrateur|Papa a aidé.
-papa|On a rangé ensemble.
+          <t>narrateur|Mila prend le cube du coussin.
+narrateur|La caisse est près du meuble.
+narrateur|Elle met le cube dans la caisse.
+narrateur|Toc.
+papa|On va ranger.
+papa|Tu ranges les cubes.
 enfant-f|Dans la caisse.
-maman|Oui. Ranger, c'est mettre dans la caisse.
-papa|Tu as fini de ranger tes jouets ?
-enfant-f|Oui.
-maman|Bravo, Mila.
-maman|C'est du bon travail.
-narrateur|Le tapis est libre.
-papa|Les pieds peuvent marcher, maintenant.
-enfant-f|Oui, papa.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+narrateur|Elle prend un cube au pied du canapé.
+narrateur|Dans la caisse.
+narrateur|Toc.
+narrateur|Elle prend la petite voiture.
+narrateur|Dans la caisse aussi.
+maman|Le coussin est libre.
+narrateur|Mila passe la main dessus.
+narrateur|C'est mou.
+enfant-f|Le livre peut s'ouvrir.
+papa|Oui. Plus de bosse.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1775,12 +1757,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Mila s'assoit près de papa. Le salon est calme. Le radiateur chante un tout petit peu. Tu veux tes chaussettes chaudes ? Oui, maman. Maman lui tend les chaussettes. Elles sont douces. La caisse est à sa place. Les cubes dorment. Oui. Dans la caisse. On reste encore un peu ensemble ? Oui. Bravo.</t>
+          <t>Maman tend les chaussettes. Elles sont douces. Elles sont chaudes. Oui. Pour le canapé. Mila s'assoit près de papa. Papa ouvre le livre. Le canard est sur l'eau. Il nage. Oui. Tout doux. La bouilloire s'est tue. Le salon est calme. Les cubes dorment. Dans la caisse. Le rond de la lampe est sur leurs genoux. On tourne la page ? Oui. Encore le canard. Papa tourne la page. Le papier fait un petit bruit. Le canard nage encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Constantin s'assoit près de papa. Le salon est calme.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman tend les chaussettes. Elles sont douces. Elles sont chaudes. Oui. Pour le canapé. Mila s'assoit près de papa. Papa ouvre le livre. Le canard est sur l'eau. Il nage. Oui. Tout doux. La bouilloire s'est tue. Le salon est calme. Les cubes dorment. Dans la caisse. Le rond de la lampe est sur leurs genoux. On tourne la page ? Oui. Encore le canard. Papa tourne la page. Le papier fait un petit bruit. Le canard nage encore.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1911,22 +1893,27 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Mila s'assoit près de papa.
+          <t>narrateur|Maman tend les chaussettes.
+narrateur|Elles sont douces.
+enfant-f|Elles sont chaudes.
+maman|Oui. Pour le canapé.
+narrateur|Mila s'assoit près de papa.
+narrateur|Papa ouvre le livre.
+narrateur|Le canard est sur l'eau.
+enfant-f|Il nage.
+papa|Oui. Tout doux.
+narrateur|La bouilloire s'est tue.
 narrateur|Le salon est calme.
-narrateur|Le radiateur chante un tout petit peu.
-maman|Tu veux tes chaussettes chaudes ?
-enfant-f|Oui, maman.
-narrateur|Maman lui tend les chaussettes.
-narrateur|Elles sont douces.
-papa|La caisse est à sa place.
-enfant-f|Les cubes dorment.
-papa|Oui. Dans la caisse.
-maman|On reste encore un peu ensemble ?
-enfant-f|Oui.
-papa|Bravo.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+maman|Les cubes dorment.
+enfant-f|Dans la caisse.
+narrateur|Le rond de la lampe est sur leurs genoux.
+papa|On tourne la page ?
+enfant-f|Oui. Encore le canard.
+narrateur|Papa tourne la page.
+narrateur|Le papier fait un petit bruit.
+maman|Le canard nage encore.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1951,12 +1938,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai mis les cubes dans la caisse. Bravo. Tu as fait du bon travail. Le radiateur reste chaud. L'histoire est finie.</t>
+          <t>On a lu le canard. Sur le canapé. Les cubes sont dans la caisse. La lampe fait encore un rond. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>On a lu le canard. Sur le canapé. Les cubes sont dans la caisse. La lampe fait encore un rond. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2091,14 +2078,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|J'ai mis les cubes dans la caisse.
-papa|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le radiateur reste chaud.
+          <t>enfant-f|On a lu le canard.
+maman|Sur le canapé.
+narrateur|Les cubes sont dans la caisse.
+papa|La lampe fait encore un rond.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2117,7 +2103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2190,6 +2176,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.RAN.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-06.xlsx
@@ -1938,12 +1938,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a lu le canard. Sur le canapé. Les cubes sont dans la caisse. La lampe fait encore un rond. L'histoire est finie.</t>
+          <t>On a lu le canard. Sur le canapé. Les cubes sont dans la caisse. La lampe fait encore un rond.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>On a lu le canard. Sur le canapé. Les cubes sont dans la caisse. La lampe fait encore un rond. L'histoire est finie.</t>
+          <t>On a lu le canard. Sur le canapé. Les cubes sont dans la caisse. La lampe fait encore un rond.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2081,8 +2081,7 @@
           <t>enfant-f|On a lu le canard.
 maman|Sur le canapé.
 narrateur|Les cubes sont dans la caisse.
-papa|La lampe fait encore un rond.
-narrateur|L'histoire est finie.</t>
+papa|La lampe fait encore un rond.</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2181,6 +2180,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.RAN.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>salon, soir, lampe du canapé</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Constantin, papa</t>
+          <t>Mila, papa, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.RAN.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-06.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le livre du canapé</t>
+          <t>Les chaussettes du radiateur</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon, soir, lampe du canapé</t>
+          <t>salon, soir, radiateur, laine et caisse de bois</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mila veut le livre sur le canapé. Un cube est sur le coussin. Elle met les cubes dans la caisse. Le livre s'ouvre.</t>
+          <t>Mila veut les chaussettes de laine près du radiateur. La tour de cubes tombe dessus. Elle cherche, met cubes et voiture dans la caisse. Les chaussettes apparaissent. Pieds au chaud, livre du canard.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La bouilloire chante tout doux. Pfff. La lampe fait un rond sur le canapé. Les mains de papa sentent le savon. L'eau est chaude, pour plus tard. Le livre est sur la table. Le livre a une couverture lisse. Un canard est dessus. Mila, en ce moment, est près du canapé. Elle touche un cube. Le cube est lisse. Je fais une petite tour. Une tour, avant le livre ? Oui. Une tour petite. Mila pose un cube. Puis un autre cube. Clic. Elle fait une petite tour. Ta tour est jolie. Elle est petite, papa. Mila pose un cube rouge. Clic. La tour grandit un peu. Elle touche le cube du haut. Le bois est tiède. Après, on lit le canard. Oui. Sur le canapé. Mila veut monter sur le canapé. Un cube est sur le coussin. Le livre ne peut pas s'ouvrir. Le livre fait une bosse. Un cube est sur le coussin. D'autres cubes sont au pied du canapé. Une petite voiture aussi. On n'a pas de place pour s'asseoir. Je voulais le canard. Le canard a besoin du coussin.</t>
+          <t>Le radiateur chante un tout petit air. Psss. Des chaussettes de laine attendent. Elles sont épaisses, près du canapé. Elles sentent le linge propre. Les chaussettes sont chaudes, papa. Oui, on les laisse près du chaud. Une caisse en bois est au salon. Elle sent un peu la forêt. En ce moment, Mila est près du canapé. Elle touche un cube. Le cube est lisse. Il est chaud, papa. C'est le radiateur, Mila. Je fais une petite tour. Une tour, avant les chaussettes ? Oui, une tour petite. Mila pose un cube. Puis un autre cube. Clic. Elle fait une petite tour. Ta tour est jolie. Elle est petite, papa. Mila pose un cube rouge. Clic. La tour grandit un peu. Ses pieds sont près du radiateur. Après, les chaussettes chaudes. Oui, pour les orteils. Mila pose encore un cube. La tour penche vers les chaussettes. Deux cubes glissent. Ils tombent sur la laine. Oh. La tour a bougé. Où sont mes chaussettes ? Sur le canapé, peut-être ? Mila monte un genou. Le coussin est vide. Dans mes mains ? Elle ouvre les paumes. Rien. Elles sont perdues. Les cubes sont encore au pied. Je veux voir dessous. Mila prend un cube. Elle le pose dans la caisse. Toc. Une petite voiture attend aussi. Elle va dans la caisse. Toc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La bouilloire chante tout doux. Pfff. La lampe fait un rond sur le canapé. Les mains de papa sentent le savon. L'eau est chaude, pour plus tard. Le livre est sur la table. Le livre a une couverture lisse. Un canard est dessus. Mila, en ce moment, est près du canapé. Elle touche un cube. Le cube est lisse. Je fais une petite tour. Une tour, avant le livre ? Oui. Une tour petite. Mila pose un cube. Puis un autre cube. Clic. Elle fait une petite tour. Ta tour est jolie. Elle est petite, papa. Mila pose un cube rouge. Clic. La tour grandit un peu. Elle touche le cube du haut. Le bois est tiède. Après, on lit le canard. Oui. Sur le canapé. Mila veut monter sur le canapé. Un cube est sur le coussin. Le livre ne peut pas s'ouvrir. Le livre fait une bosse. Un cube est sur le coussin. D'autres cubes sont au pied du canapé. Une petite voiture aussi. On n'a pas de place pour s'asseoir. Je voulais le canard. Le canard a besoin du coussin.</t>
+          <t>Le radiateur chante un tout petit air. Psss. Des chaussettes de laine attendent. Elles sont épaisses, près du canapé. Elles sentent le linge propre. Les chaussettes sont chaudes, papa. Oui, on les laisse près du chaud. Une caisse en bois est au salon. Elle sent un peu la forêt. En ce moment, Mila est près du canapé. Elle touche un cube. Le cube est lisse. Il est chaud, papa. C'est le radiateur, Mila. Je fais une petite tour. Une tour, avant les chaussettes ? Oui, une tour petite. Mila pose un cube. Puis un autre cube. Clic. Elle fait une petite tour. Ta tour est jolie. Elle est petite, papa. Mila pose un cube rouge. Clic. La tour grandit un peu. Ses pieds sont près du radiateur. Après, les chaussettes chaudes. Oui, pour les orteils. Mila pose encore un cube. La tour penche vers les chaussettes. Deux cubes glissent. Ils tombent sur la laine. Oh. La tour a bougé. Où sont mes chaussettes ? Sur le canapé, peut-être ? Mila monte un genou. Le coussin est vide. Dans mes mains ? Elle ouvre les paumes. Rien. Elles sont perdues. Les cubes sont encore au pied. Je veux voir dessous. Mila prend un cube. Elle le pose dans la caisse. Toc. Une petite voiture attend aussi. Elle va dans la caisse. Toc.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1245,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,20 +1324,23 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La bouilloire chante tout doux.
-narrateur|Pfff.
-narrateur|La lampe fait un rond sur le canapé.
-narrateur|Les mains de papa sentent le savon.
-maman|L'eau est chaude, pour plus tard.
-papa|Le livre est sur la table.
-narrateur|Le livre a une couverture lisse.
-narrateur|Un canard est dessus.
-narrateur|Mila, en ce moment, est près du canapé.
+          <t>narrateur|Le radiateur chante un tout petit air.
+narrateur|Psss.
+narrateur|Des chaussettes de laine attendent.
+narrateur|Elles sont épaisses, près du canapé.
+narrateur|Elles sentent le linge propre.
+maman|Les chaussettes sont chaudes, papa.
+papa|Oui, on les laisse près du chaud.
+narrateur|Une caisse en bois est au salon.
+narrateur|Elle sent un peu la forêt.
+narrateur|En ce moment, Mila est près du canapé.
 narrateur|Elle touche un cube.
 narrateur|Le cube est lisse.
+enfant-f|Il est chaud, papa.
+papa|C'est le radiateur, Mila.
 enfant-f|Je fais une petite tour.
-maman|Une tour, avant le livre ?
-enfant-f|Oui. Une tour petite.
+maman|Une tour, avant les chaussettes ?
+enfant-f|Oui, une tour petite.
 narrateur|Mila pose un cube.
 narrateur|Puis un autre cube.
 narrateur|Clic.
@@ -1347,20 +1350,31 @@
 narrateur|Mila pose un cube rouge.
 narrateur|Clic.
 narrateur|La tour grandit un peu.
-narrateur|Elle touche le cube du haut.
-narrateur|Le bois est tiède.
-enfant-f|Après, on lit le canard.
-papa|Oui. Sur le canapé.
-narrateur|Mila veut monter sur le canapé.
-narrateur|Un cube est sur le coussin.
-narrateur|Le livre ne peut pas s'ouvrir.
-enfant-f|Le livre fait une bosse.
-maman|Un cube est sur le coussin.
-narrateur|D'autres cubes sont au pied du canapé.
-narrateur|Une petite voiture aussi.
-papa|On n'a pas de place pour s'asseoir.
-enfant-f|Je voulais le canard.
-maman|Le canard a besoin du coussin.</t>
+narrateur|Ses pieds sont près du radiateur.
+enfant-f|Après, les chaussettes chaudes.
+maman|Oui, pour les orteils.
+narrateur|Mila pose encore un cube.
+narrateur|La tour penche vers les chaussettes.
+narrateur|Deux cubes glissent.
+narrateur|Ils tombent sur la laine.
+enfant-f|Oh.
+papa|La tour a bougé.
+enfant-f|Où sont mes chaussettes ?
+maman|Sur le canapé, peut-être ?
+narrateur|Mila monte un genou.
+narrateur|Le coussin est vide.
+enfant-f|Dans mes mains ?
+narrateur|Elle ouvre les paumes.
+narrateur|Rien.
+enfant-f|Elles sont perdues.
+papa|Les cubes sont encore au pied.
+enfant-f|Je veux voir dessous.
+narrateur|Mila prend un cube.
+narrateur|Elle le pose dans la caisse.
+narrateur|Toc.
+narrateur|Une petite voiture attend aussi.
+narrateur|Elle va dans la caisse.
+narrateur|Toc.</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1401,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le jeu est fini. Que fait Mila ?</t>
+          <t>Mila cherche ses chaussettes. Où sont-elles ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Le jeu est fini. Que fait Mila ?</t>
+          <t>Mila cherche ses chaussettes. Où sont-elles ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1402,12 +1416,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>les chaussettes</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>ranger | la caisse | dans la caisse | elle range</t>
+          <t>les chaussettes | chaussettes | la laine | sous la tour | sous les cubes | dessous</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1422,7 +1436,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle met les cubes dans la caisse. Que fait Mila ?</t>
+          <t>Elle cherche sous les cubes. Où sont les chaussettes ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1471,7 +1485,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1543,7 +1557,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le jeu est fini. Que fait Mila ?</t>
+          <t>narrateur|Mila cherche ses chaussettes.
+narrateur|Où sont-elles ?</t>
         </is>
       </c>
     </row>
@@ -1570,12 +1585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila prend le cube du coussin. La caisse est près du meuble. Elle met le cube dans la caisse. Toc. On va ranger. Tu ranges les cubes. Dans la caisse. Elle prend un cube au pied du canapé. Dans la caisse. Toc. Elle prend la petite voiture. Dans la caisse aussi. Le coussin est libre. Mila passe la main dessus. C'est mou. Le livre peut s'ouvrir. Oui. Plus de bosse.</t>
+          <t>Un cube rouge reste au sol. Mila le glisse dans la caisse. Toc. Tu regardes bien sous la tour ? Oui, maman. Un bout de tapis reparaît. Encore un, tout doux. Mila écarte le dernier cube. Un coin de laine épaisse. Mes chaussettes ! Les chaussettes étaient sous la tour. Elles sont encore chaudes. Mila les serre contre sa joue. La laine sent le savon. Merci, tu les as trouvées. Te voilà, petite laine. Elles étaient dessous. La caisse a les cubes, maintenant. Le tapis près du radiateur est libre. Le radiateur chante encore un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Mila prend le cube du coussin. La caisse est près du meuble. Elle met le cube dans la caisse. Toc. On va ranger. Tu ranges les cubes. Dans la caisse. Elle prend un cube au pied du canapé. Dans la caisse. Toc. Elle prend la petite voiture. Dans la caisse aussi. Le coussin est libre. Mila passe la main dessus. C'est mou. Le livre peut s'ouvrir. Oui. Plus de bosse.</t>
+          <t>Un cube rouge reste au sol. Mila le glisse dans la caisse. Toc. Tu regardes bien sous la tour ? Oui, maman. Un bout de tapis reparaît. Encore un, tout doux. Mila écarte le dernier cube. Un coin de laine épaisse. Mes chaussettes ! Les chaussettes étaient sous la tour. Elles sont encore chaudes. Mila les serre contre sa joue. La laine sent le savon. Merci, tu les as trouvées. Te voilà, petite laine. Elles étaient dessous. La caisse a les cubes, maintenant. Le tapis près du radiateur est libre. Le radiateur chante encore un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1631,14 +1646,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1714,23 +1729,26 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Mila prend le cube du coussin.
-narrateur|La caisse est près du meuble.
-narrateur|Elle met le cube dans la caisse.
+          <t>narrateur|Un cube rouge reste au sol.
+narrateur|Mila le glisse dans la caisse.
 narrateur|Toc.
-papa|On va ranger.
-papa|Tu ranges les cubes.
-enfant-f|Dans la caisse.
-narrateur|Elle prend un cube au pied du canapé.
-narrateur|Dans la caisse.
-narrateur|Toc.
-narrateur|Elle prend la petite voiture.
-narrateur|Dans la caisse aussi.
-maman|Le coussin est libre.
-narrateur|Mila passe la main dessus.
-narrateur|C'est mou.
-enfant-f|Le livre peut s'ouvrir.
-papa|Oui. Plus de bosse.</t>
+maman|Tu regardes bien sous la tour ?
+enfant-f|Oui, maman.
+narrateur|Un bout de tapis reparaît.
+papa|Encore un, tout doux.
+narrateur|Mila écarte le dernier cube.
+narrateur|Un coin de laine épaisse.
+enfant-f|Mes chaussettes !
+narrateur|Les chaussettes étaient sous la tour.
+narrateur|Elles sont encore chaudes.
+narrateur|Mila les serre contre sa joue.
+narrateur|La laine sent le savon.
+papa|Merci, tu les as trouvées.
+maman|Te voilà, petite laine.
+enfant-f|Elles étaient dessous.
+narrateur|La caisse a les cubes, maintenant.
+narrateur|Le tapis près du radiateur est libre.
+narrateur|Le radiateur chante encore un peu.</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1775,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman tend les chaussettes. Elles sont douces. Elles sont chaudes. Oui. Pour le canapé. Mila s'assoit près de papa. Papa ouvre le livre. Le canard est sur l'eau. Il nage. Oui. Tout doux. La bouilloire s'est tue. Le salon est calme. Les cubes dorment. Dans la caisse. Le rond de la lampe est sur leurs genoux. On tourne la page ? Oui. Encore le canard. Papa tourne la page. Le papier fait un petit bruit. Le canard nage encore.</t>
+          <t>Maman tend les chaussettes. Mila enfile la première. Puis la deuxième. Elles sont douces. Les orteils sont au chaud. Mila s'assoit près du radiateur. Le métal chante tout bas. On reste un moment ? Oui, maman. Ses pieds touchent le tapis libre. La laine est épaisse, un peu lourde. Tu veux le livre du canard ? Oui, papa. Papa ouvre le livre. La couverture est lisse. Mila pose un pied sur l'autre. Les chaussettes restent bien chaudes.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Maman tend les chaussettes. Elles sont douces. Elles sont chaudes. Oui. Pour le canapé. Mila s'assoit près de papa. Papa ouvre le livre. Le canard est sur l'eau. Il nage. Oui. Tout doux. La bouilloire s'est tue. Le salon est calme. Les cubes dorment. Dans la caisse. Le rond de la lampe est sur leurs genoux. On tourne la page ? Oui. Encore le canard. Papa tourne la page. Le papier fait un petit bruit. Le canard nage encore.</t>
+          <t>Maman tend les chaussettes. Mila enfile la première. Puis la deuxième. Elles sont douces. Les orteils sont au chaud. Mila s'assoit près du radiateur. Le métal chante tout bas. On reste un moment ? Oui, maman. Ses pieds touchent le tapis libre. La laine est épaisse, un peu lourde. Tu veux le livre du canard ? Oui, papa. Papa ouvre le livre. La couverture est lisse. Mila pose un pied sur l'autre. Les chaussettes restent bien chaudes.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1818,14 +1836,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1894,24 +1912,22 @@
       <c r="AW5" t="inlineStr">
         <is>
           <t>narrateur|Maman tend les chaussettes.
-narrateur|Elles sont douces.
-enfant-f|Elles sont chaudes.
-maman|Oui. Pour le canapé.
-narrateur|Mila s'assoit près de papa.
+narrateur|Mila enfile la première.
+narrateur|Puis la deuxième.
+enfant-f|Elles sont douces.
+papa|Les orteils sont au chaud.
+narrateur|Mila s'assoit près du radiateur.
+narrateur|Le métal chante tout bas.
+maman|On reste un moment ?
+enfant-f|Oui, maman.
+narrateur|Ses pieds touchent le tapis libre.
+narrateur|La laine est épaisse, un peu lourde.
+papa|Tu veux le livre du canard ?
+enfant-f|Oui, papa.
 narrateur|Papa ouvre le livre.
-narrateur|Le canard est sur l'eau.
-enfant-f|Il nage.
-papa|Oui. Tout doux.
-narrateur|La bouilloire s'est tue.
-narrateur|Le salon est calme.
-maman|Les cubes dorment.
-enfant-f|Dans la caisse.
-narrateur|Le rond de la lampe est sur leurs genoux.
-papa|On tourne la page ?
-enfant-f|Oui. Encore le canard.
-narrateur|Papa tourne la page.
-narrateur|Le papier fait un petit bruit.
-maman|Le canard nage encore.</t>
+narrateur|La couverture est lisse.
+narrateur|Mila pose un pied sur l'autre.
+narrateur|Les chaussettes restent bien chaudes.</t>
         </is>
       </c>
     </row>
@@ -1938,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a lu le canard. Sur le canapé. Les cubes sont dans la caisse. La lampe fait encore un rond.</t>
+          <t>Mes pieds sont au chaud. La laine a été retrouvée. Bravo, tu les as trouvées. Le radiateur chante encore. La laine reste douce sur les orteils.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>On a lu le canard. Sur le canapé. Les cubes sont dans la caisse. La lampe fait encore un rond.</t>
+          <t>Mes pieds sont au chaud. La laine a été retrouvée. Bravo, tu les as trouvées. Le radiateur chante encore. La laine reste douce sur les orteils.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1999,14 +2015,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2078,10 +2094,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|On a lu le canard.
-maman|Sur le canapé.
-narrateur|Les cubes sont dans la caisse.
-papa|La lampe fait encore un rond.</t>
+          <t>enfant-f|Mes pieds sont au chaud.
+maman|La laine a été retrouvée.
+papa|Bravo, tu les as trouvées.
+narrateur|Le radiateur chante encore.
+narrateur|La laine reste douce sur les orteils.</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2187,6 +2204,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.RAN.001-06.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-06.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mila veut les chaussettes de laine près du radiateur. La tour de cubes tombe dessus. Elle cherche, met cubes et voiture dans la caisse. Les chaussettes apparaissent. Pieds au chaud, livre du canard.</t>
+          <t>Au campement du radiateur, un éclat de laine brille sur le métal. Mila veut les chaussettes chaudes, maintenant. La tour penche : les cubes tombent sur la laine. Elle cherche le canapé, les paumes, puis saisit toute la pile : les cubes s'éparpillent. Elle refuse de foncer, pose un cube, retrouve la laine. Sur l'orteil, l'éclat de laine tient.</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le radiateur chante un tout petit air. Psss. Des chaussettes de laine attendent. Elles sont épaisses, près du canapé. Elles sentent le linge propre. Les chaussettes sont chaudes, papa. Oui, on les laisse près du chaud. Une caisse en bois est au salon. Elle sent un peu la forêt. En ce moment, Mila est près du canapé. Elle touche un cube. Le cube est lisse. Il est chaud, papa. C'est le radiateur, Mila. Je fais une petite tour. Une tour, avant les chaussettes ? Oui, une tour petite. Mila pose un cube. Puis un autre cube. Clic. Elle fait une petite tour. Ta tour est jolie. Elle est petite, papa. Mila pose un cube rouge. Clic. La tour grandit un peu. Ses pieds sont près du radiateur. Après, les chaussettes chaudes. Oui, pour les orteils. Mila pose encore un cube. La tour penche vers les chaussettes. Deux cubes glissent. Ils tombent sur la laine. Oh. La tour a bougé. Où sont mes chaussettes ? Sur le canapé, peut-être ? Mila monte un genou. Le coussin est vide. Dans mes mains ? Elle ouvre les paumes. Rien. Elles sont perdues. Les cubes sont encore au pied. Je veux voir dessous. Mila prend un cube. Elle le pose dans la caisse. Toc. Une petite voiture attend aussi. Elle va dans la caisse. Toc.</t>
+          <t>Le métal du radiateur fait psss. Une lampe ronde pose un halo. Mila connaît ce salon, le soir. Un détail paraît nouveau, sur le métal. Au campement du radiateur, ça sent le bois. Des chaussettes de laine attendent. Elles sont épaisses, près du canapé. Sur le bord, un éclat de laine brille. Il est petit, papa. C'est un éclat de laine. La laine sent le linge propre. Les chaussettes sont chaudes, Mila. On les laisse près du chaud. Une caisse en bois est là. Elle sent un peu la forêt. Le tapis est froid, sous les orteils. J'ai froid aux pieds ! Je veux les chaussettes, maintenant ! Avant la tour de cubes ? Non, les chaussettes d'abord ! En ce moment, Mila saisit la laine. La laine est chaude, un peu lourde. Un cube rouge attend au sol. Une tour petite, aussi ! Elle pose un cube trop vite. Ça fait clic, contre le tapis. Puis un cube jaune. Ça fait clic, contre le rouge. Ta tour est jolie. Elle est petite, papa. Mila pose un cube de plus. La tour penche vers la laine. Deux cubes glissent. Ils tombent sur les chaussettes. Oh. Le sourire de Mila disparaît. Dans sa poitrine, envie et inquiétude se bousculent. Où sont mes chaussettes ? Sur le canapé, peut-être ? Mila monte un genou. Le coussin est vide. Dans mes mains ? Elle ouvre les paumes. Rien. Elles sont perdues. Je prends tout, d'un coup ! Elle saisit la pile trop vite. Les cubes glissent entre ses doigts. Le tapis disparaît sous les cubes. Ça ne veut pas, papa. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu regardes sous les cubes ?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Le radiateur chante un tout petit air. Psss. Des chaussettes de laine attendent. Elles sont épaisses, près du canapé. Elles sentent le linge propre. Les chaussettes sont chaudes, papa. Oui, on les laisse près du chaud. Une caisse en bois est au salon. Elle sent un peu la forêt. En ce moment, Mila est près du canapé. Elle touche un cube. Le cube est lisse. Il est chaud, papa. C'est le radiateur, Mila. Je fais une petite tour. Une tour, avant les chaussettes ? Oui, une tour petite. Mila pose un cube. Puis un autre cube. Clic. Elle fait une petite tour. Ta tour est jolie. Elle est petite, papa. Mila pose un cube rouge. Clic. La tour grandit un peu. Ses pieds sont près du radiateur. Après, les chaussettes chaudes. Oui, pour les orteils. Mila pose encore un cube. La tour penche vers les chaussettes. Deux cubes glissent. Ils tombent sur la laine. Oh. La tour a bougé. Où sont mes chaussettes ? Sur le canapé, peut-être ? Mila monte un genou. Le coussin est vide. Dans mes mains ? Elle ouvre les paumes. Rien. Elles sont perdues. Les cubes sont encore au pied. Je veux voir dessous. Mila prend un cube. Elle le pose dans la caisse. Toc. Une petite voiture attend aussi. Elle va dans la caisse. Toc.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le métal du radiateur fait psss. Une lampe ronde pose un halo. Mila connaît ce salon, le soir. Un détail paraît nouveau, sur le métal. Au campement du radiateur, ça sent le bois. Des chaussettes de laine attendent. Elles sont épaisses, près du canapé. Sur le bord, un &lt;emphasis level="moderate"&gt;éclat de laine&lt;/emphasis&gt; brille. Il est petit, papa. C'est un éclat de laine. La laine sent le linge propre. Les chaussettes sont chaudes, Mila. On les laisse près du chaud. Une caisse en bois est là. Elle sent un peu la forêt. Le tapis est froid, sous les orteils. J'ai froid aux pieds ! Je veux les chaussettes, maintenant ! Avant la tour de cubes ? Non, les chaussettes d'abord ! En ce moment, Mila saisit la laine. La laine est chaude, un peu lourde. Un cube rouge attend au sol. Une tour petite, aussi ! Elle pose un cube trop vite. Ça fait clic, contre le tapis. Puis un cube jaune. Ça fait clic, contre le rouge. Ta tour est jolie. Elle est petite, papa. Mila pose un cube de plus. La tour penche vers la laine. Deux cubes glissent. Ils tombent sur les chaussettes. Oh. Le sourire de Mila disparaît. Dans sa poitrine, envie et inquiétude se bousculent. Où sont mes chaussettes ? Sur le canapé, peut-être ? Mila monte un genou. Le coussin est vide. Dans mes mains ? Elle ouvre les paumes. Rien. Elles sont perdues. Je prends tout, d'un coup ! Elle saisit la pile trop vite. Les cubes glissent entre ses doigts. Le tapis disparaît sous les cubes. Ça ne veut pas, papa. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu regardes sous les cubes ?&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Constantin joue dans le salon. Les cubes sont partout. Papa dit : on range. Les jouets retournent dans la caisse. Constantin prend un cube. Il le met dans la caisse. Il prend une voiture. Il la met dans la caisse. Papa aide. Ils rangent ensemble. La caisse se remplit. Le tapis redevient vide. Constantin dit : j'ai rangé. Papa sourit. Constantin pousse la caisse. La caisse va près du meuble. &lt;emphasis&gt;ranger&lt;/emphasis&gt;, c'est mettre dans la caisse. Papa dit : merci. Constantin tape des mains.&lt;/slow&gt; [pause]</t>
+          <t>Le métal du radiateur fait psss. Une lampe ronde pose un halo. Mila connaît ce salon, le soir. Un détail paraît nouveau, sur le métal. Au campement du radiateur, ça sent le bois. Des chaussettes de laine attendent. Elles sont épaisses, près du canapé. Sur le bord, un &lt;emphasis&gt;éclat de laine&lt;/emphasis&gt; brille. Il est petit, papa. C'est un éclat de laine. La laine sent le linge propre. Les chaussettes sont chaudes, Mila. On les laisse près du chaud. Une caisse en bois est là. Elle sent un peu la forêt. Le tapis est froid, sous les orteils. J'ai froid aux pieds ! Je veux les chaussettes, maintenant ! Avant la tour de cubes ? Non, les chaussettes d'abord ! En ce moment, Mila saisit la laine. La laine est chaude, un peu lourde. Un cube rouge attend au sol. Une tour petite, aussi ! Elle pose un cube trop vite. Ça fait clic, contre le tapis. Puis un cube jaune. Ça fait clic, contre le rouge. Ta tour est jolie. Elle est petite, papa. Mila pose un cube de plus. La tour penche vers la laine. Deux cubes glissent. Ils tombent sur les chaussettes. Oh. Le sourire de Mila disparaît. Dans sa poitrine, envie et inquiétude se bousculent. Où sont mes chaussettes ? Sur le canapé, peut-être ? Mila monte un genou. Le coussin est vide. Dans mes mains ? Elle ouvre les paumes. Rien. Elles sont perdues. Je prends tout, d'un coup ! Elle saisit la pile trop vite. Les cubes glissent entre ses doigts. Le tapis disparaît sous les cubes. Ça ne veut pas, papa. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu regardes sous les cubes ? [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1275,30 +1275,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>éclat de laine</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1319,46 +1319,52 @@
         <v>50</v>
       </c>
       <c r="AU2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis découragement; intensite=2; destinataire=enfant; sous_texte=elle_veut_les_chaussettes_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le radiateur chante un tout petit air.
-narrateur|Psss.
+          <t>narrateur|Le métal du radiateur fait psss.
+narrateur|Une lampe ronde pose un halo.
+narrateur|Mila connaît ce salon, le soir.
+narrateur|Un détail paraît nouveau, sur le métal.
+narrateur|Au campement du radiateur, ça sent le bois.
 narrateur|Des chaussettes de laine attendent.
 narrateur|Elles sont épaisses, près du canapé.
-narrateur|Elles sentent le linge propre.
-maman|Les chaussettes sont chaudes, papa.
-papa|Oui, on les laisse près du chaud.
-narrateur|Une caisse en bois est au salon.
+narrateur|Sur le bord, un éclat de laine brille.
+enfant-f|Il est petit, papa.
+papa|C'est un éclat de laine.
+narrateur|La laine sent le linge propre.
+maman|Les chaussettes sont chaudes, Mila.
+papa|On les laisse près du chaud.
+narrateur|Une caisse en bois est là.
 narrateur|Elle sent un peu la forêt.
-narrateur|En ce moment, Mila est près du canapé.
-narrateur|Elle touche un cube.
-narrateur|Le cube est lisse.
-enfant-f|Il est chaud, papa.
-papa|C'est le radiateur, Mila.
-enfant-f|Je fais une petite tour.
-maman|Une tour, avant les chaussettes ?
-enfant-f|Oui, une tour petite.
-narrateur|Mila pose un cube.
-narrateur|Puis un autre cube.
-narrateur|Clic.
-narrateur|Elle fait une petite tour.
+narrateur|Le tapis est froid, sous les orteils.
+enfant-f|J'ai froid aux pieds !
+enfant-f|Je veux les chaussettes, maintenant !
+maman|Avant la tour de cubes ?
+enfant-f|Non, les chaussettes d'abord !
+narrateur|En ce moment, Mila saisit la laine.
+narrateur|La laine est chaude, un peu lourde.
+narrateur|Un cube rouge attend au sol.
+enfant-f|Une tour petite, aussi !
+narrateur|Elle pose un cube trop vite.
+narrateur|Ça fait clic, contre le tapis.
+narrateur|Puis un cube jaune.
+narrateur|Ça fait clic, contre le rouge.
 papa|Ta tour est jolie.
 enfant-f|Elle est petite, papa.
-narrateur|Mila pose un cube rouge.
-narrateur|Clic.
-narrateur|La tour grandit un peu.
-narrateur|Ses pieds sont près du radiateur.
-enfant-f|Après, les chaussettes chaudes.
-maman|Oui, pour les orteils.
-narrateur|Mila pose encore un cube.
-narrateur|La tour penche vers les chaussettes.
+narrateur|Mila pose un cube de plus.
+narrateur|La tour penche vers la laine.
 narrateur|Deux cubes glissent.
-narrateur|Ils tombent sur la laine.
+narrateur|Ils tombent sur les chaussettes.
 enfant-f|Oh.
-papa|La tour a bougé.
+narrateur|Le sourire de Mila disparaît.
+narrateur|Dans sa poitrine, envie et inquiétude se bousculent.
 enfant-f|Où sont mes chaussettes ?
 maman|Sur le canapé, peut-être ?
 narrateur|Mila monte un genou.
@@ -1367,14 +1373,19 @@
 narrateur|Elle ouvre les paumes.
 narrateur|Rien.
 enfant-f|Elles sont perdues.
-papa|Les cubes sont encore au pied.
-enfant-f|Je veux voir dessous.
-narrateur|Mila prend un cube.
-narrateur|Elle le pose dans la caisse.
-narrateur|Toc.
-narrateur|Une petite voiture attend aussi.
-narrateur|Elle va dans la caisse.
-narrateur|Toc.</t>
+enfant-f|Je prends tout, d'un coup !
+narrateur|Elle saisit la pile trop vite.
+narrateur|Les cubes glissent entre ses doigts.
+narrateur|Le tapis disparaît sous les cubes.
+enfant-f|Ça ne veut pas, papa.
+narrateur|Ses épaules tombent un peu.
+narrateur|Papa se baisse à sa hauteur.
+papa|Tu regardes sous les cubes ?</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>radiateur,laine</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1417,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Mila cherche ses chaussettes. Où sont-elles ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Mila cherche ses &lt;emphasis level="moderate"&gt;chaussettes&lt;/emphasis&gt;. Où sont-elles ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Le jeu est fini. Que fait Constantin ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Mila cherche ses &lt;emphasis&gt;chaussettes&lt;/emphasis&gt;. Où sont-elles ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1474,7 +1485,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1482,10 +1493,10 @@
         </is>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1500,34 +1511,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>chaussettes</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>380</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1536,13 +1551,13 @@
         </is>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
@@ -1552,7 +1567,7 @@
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=les_chaussettes_sont_sous_les_cubes; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1585,17 +1600,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Un cube rouge reste au sol. Mila le glisse dans la caisse. Toc. Tu regardes bien sous la tour ? Oui, maman. Un bout de tapis reparaît. Encore un, tout doux. Mila écarte le dernier cube. Un coin de laine épaisse. Mes chaussettes ! Les chaussettes étaient sous la tour. Elles sont encore chaudes. Mila les serre contre sa joue. La laine sent le savon. Merci, tu les as trouvées. Te voilà, petite laine. Elles étaient dessous. La caisse a les cubes, maintenant. Le tapis près du radiateur est libre. Le radiateur chante encore un peu.</t>
+          <t>Mila refuse de prendre toute la pile. Elle pose un genou au tapis. Un cube rouge reste près de sa main. Je le mets toute seule. Elle glisse le cube dans la caisse. Toc. Le bois sent un peu la forêt. Tu regardes bien dessous ? Oui, maman. La tour devient plus petite. Un bout de tapis reparaît. Le cube jaune va dans la caisse. Toc. Je sors le reste, d'un coup ! Elle tire trop fort sur un cube. Deux cubes retombent, comme un toit. Oh. Mila ne reprend pas trop vite. Elle écoute le salon, un instant. Le radiateur fait psss, près d'elle. Sous un cube, un éclat de laine brille. Il est là. Mila refuse de foncer. Elle écarte un cube, lentement. Un coin de laine épaisse. Mes chaussettes ! Les chaussettes étaient sous la tour. Elles sentent le savon, un peu chaud. Mila les serre contre sa joue. Merci, Mila. Elles étaient dessous. La caisse a presque tous les cubes. Une petite voiture va dedans. Toc. Le tapis est libre, près du chaud. La laine peut s'enfiler ? Oui, maman. Mila pose la main sur la laine. Le tissu est un peu rêche.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Un cube rouge reste au sol. Mila le glisse dans la caisse. Toc. Tu regardes bien sous la tour ? Oui, maman. Un bout de tapis reparaît. Encore un, tout doux. Mila écarte le dernier cube. Un coin de laine épaisse. Mes chaussettes ! Les chaussettes étaient sous la tour. Elles sont encore chaudes. Mila les serre contre sa joue. La laine sent le savon. Merci, tu les as trouvées. Te voilà, petite laine. Elles étaient dessous. La caisse a les cubes, maintenant. Le tapis près du radiateur est libre. Le radiateur chante encore un peu.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Mila refuse de prendre toute la pile. Elle pose un genou au tapis. Un cube rouge reste près de sa main. Je le mets toute seule. Elle glisse le cube dans la &lt;emphasis level="moderate"&gt;caisse&lt;/emphasis&gt;. Toc. Le bois sent un peu la forêt. Tu regardes bien dessous ? Oui, maman. La tour devient plus petite. Un bout de tapis reparaît. Le cube jaune va dans la caisse. Toc. Je sors le reste, d'un coup ! Elle tire trop fort sur un cube. Deux cubes retombent, comme un toit. Oh. Mila ne reprend pas trop vite. Elle écoute le salon, un instant. Le radiateur fait psss, près d'elle. Sous un cube, un éclat de laine brille. Il est là. Mila refuse de foncer. Elle écarte un cube, lentement. Un coin de laine épaisse. Mes chaussettes ! Les chaussettes étaient sous la tour. Elles sentent le savon, un peu chaud. Mila les serre contre sa joue. Merci, Mila. Elles étaient dessous. La caisse a presque tous les cubes. Une petite voiture va dedans. Toc. Le tapis est libre, près du chaud. La laine peut s'enfiler ? Oui, maman. Mila pose la main sur la laine. Le tissu est un peu rêche.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Constantin a rangé. Les cubes sont dans la &lt;emphasis&gt;caisse&lt;/emphasis&gt;. Papa a aidé.&lt;/slow&gt; [pause]</t>
+          <t>Mila refuse de prendre toute la pile. Elle pose un genou au tapis. Un cube rouge reste près de sa main. Je le mets toute seule. Elle glisse le cube dans la &lt;emphasis&gt;caisse&lt;/emphasis&gt;. Toc. Le bois sent un peu la forêt. Tu regardes bien dessous ? Oui, maman. La tour devient plus petite. Un bout de tapis reparaît. Le cube jaune va dans la caisse. Toc. Je sors le reste, d'un coup ! Elle tire trop fort sur un cube. Deux cubes retombent, comme un toit. Oh. Mila ne reprend pas trop vite. Elle écoute le salon, un instant. Le radiateur fait psss, près d'elle. Sous un cube, un éclat de laine brille. Il est là. Mila refuse de foncer. Elle écarte un cube, lentement. Un coin de laine épaisse. Mes chaussettes ! Les chaussettes étaient sous la tour. Elles sentent le savon, un peu chaud. Mila les serre contre sa joue. Merci, Mila. Elles étaient dessous. La caisse a presque tous les cubes. Une petite voiture va dedans. Toc. Le tapis est libre, près du chaud. La laine peut s'enfiler ? Oui, maman. Mila pose la main sur la laine. Le tissu est un peu rêche. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1642,7 +1657,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1650,10 +1665,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1683,23 +1698,23 @@
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>380</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1708,10 +1723,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1720,35 +1735,59 @@
         <v>50</v>
       </c>
       <c r="AU4" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=concentration puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=elle_pose_un_cube_sans_foncer; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Un cube rouge reste au sol.
-narrateur|Mila le glisse dans la caisse.
+          <t>narrateur|Mila refuse de prendre toute la pile.
+narrateur|Elle pose un genou au tapis.
+narrateur|Un cube rouge reste près de sa main.
+enfant-f|Je le mets toute seule.
+narrateur|Elle glisse le cube dans la caisse.
 narrateur|Toc.
-maman|Tu regardes bien sous la tour ?
+narrateur|Le bois sent un peu la forêt.
+maman|Tu regardes bien dessous ?
 enfant-f|Oui, maman.
+narrateur|La tour devient plus petite.
 narrateur|Un bout de tapis reparaît.
-papa|Encore un, tout doux.
-narrateur|Mila écarte le dernier cube.
+narrateur|Le cube jaune va dans la caisse.
+narrateur|Toc.
+enfant-f|Je sors le reste, d'un coup !
+narrateur|Elle tire trop fort sur un cube.
+narrateur|Deux cubes retombent, comme un toit.
+enfant-f|Oh.
+narrateur|Mila ne reprend pas trop vite.
+narrateur|Elle écoute le salon, un instant.
+narrateur|Le radiateur fait psss, près d'elle.
+narrateur|Sous un cube, un éclat de laine brille.
+enfant-f|Il est là.
+narrateur|Mila refuse de foncer.
+narrateur|Elle écarte un cube, lentement.
 narrateur|Un coin de laine épaisse.
 enfant-f|Mes chaussettes !
 narrateur|Les chaussettes étaient sous la tour.
-narrateur|Elles sont encore chaudes.
+narrateur|Elles sentent le savon, un peu chaud.
 narrateur|Mila les serre contre sa joue.
-narrateur|La laine sent le savon.
-papa|Merci, tu les as trouvées.
-maman|Te voilà, petite laine.
+papa|Merci, Mila.
 enfant-f|Elles étaient dessous.
-narrateur|La caisse a les cubes, maintenant.
-narrateur|Le tapis près du radiateur est libre.
-narrateur|Le radiateur chante encore un peu.</t>
+narrateur|La caisse a presque tous les cubes.
+narrateur|Une petite voiture va dedans.
+narrateur|Toc.
+narrateur|Le tapis est libre, près du chaud.
+maman|La laine peut s'enfiler ?
+enfant-f|Oui, maman.
+narrateur|Mila pose la main sur la laine.
+narrateur|Le tissu est un peu rêche.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>caisse,bois</t>
         </is>
       </c>
     </row>
@@ -1775,17 +1814,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman tend les chaussettes. Mila enfile la première. Puis la deuxième. Elles sont douces. Les orteils sont au chaud. Mila s'assoit près du radiateur. Le métal chante tout bas. On reste un moment ? Oui, maman. Ses pieds touchent le tapis libre. La laine est épaisse, un peu lourde. Tu veux le livre du canard ? Oui, papa. Papa ouvre le livre. La couverture est lisse. Mila pose un pied sur l'autre. Les chaussettes restent bien chaudes.</t>
+          <t>On enfile les chaussettes ? Maman tend la première. Mila pousse le pied, trop vite. La laine se plie, de travers. Elle ne veut pas ! Mila veut foncer, d'un coup. Mila refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. Personne ne dit la suite. Elle regarde le bord de laine. Un éclat de laine brille, au revers. Comme sur le métal ! Tu le vois, toi ? Oui, sur ce bord. Mila tourne la chaussette, lente. Elle écoute le radiateur, un instant. Psss. Le pied glisse, sans forcer. Elle est dedans. Et l'autre ? La deuxième suit, sans se presser. Les orteils sont au chaud ? Oui, papa. Mila s'assoit près du radiateur. Le métal chante, petit. Tu veux le livre du canard ? Oui, papa. Papa ouvre le livre. La couverture est lisse. Les pieds touchent le tapis libre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Maman tend les chaussettes. Mila enfile la première. Puis la deuxième. Elles sont douces. Les orteils sont au chaud. Mila s'assoit près du radiateur. Le métal chante tout bas. On reste un moment ? Oui, maman. Ses pieds touchent le tapis libre. La laine est épaisse, un peu lourde. Tu veux le livre du canard ? Oui, papa. Papa ouvre le livre. La couverture est lisse. Mila pose un pied sur l'autre. Les chaussettes restent bien chaudes.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;On enfile les chaussettes ? Maman tend la première. Mila pousse le pied, trop vite. La laine se plie, de travers. Elle ne veut pas ! Mila veut foncer, d'un coup. Mila refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. Personne ne dit la suite. Elle regarde le bord de laine. Un &lt;emphasis level="moderate"&gt;éclat de laine&lt;/emphasis&gt; brille, au revers. Comme sur le métal ! Tu le vois, toi ? Oui, sur ce bord. Mila tourne la chaussette, lente. Elle écoute le radiateur, un instant. Psss. Le pied glisse, sans forcer. Elle est dedans. Et l'autre ? La deuxième suit, sans se presser. Les orteils sont au chaud ? Oui, papa. Mila s'assoit près du radiateur. Le métal chante, petit. Tu veux le livre du canard ? Oui, papa. Papa ouvre le livre. La couverture est lisse. Les pieds touchent le tapis libre.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Constantin s'assoit près de papa. Le salon est calme.&lt;/slow&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;On enfile les chaussettes ? Maman tend la première. Mila pousse le pied, trop vite. La laine se plie, de travers. Elle ne veut pas ! Mila veut foncer, d'un coup. Mila refuse de foncer. Ses épaules se serrent un peu. Ça tape, dans sa poitrine. Personne ne dit la suite. Elle regarde le bord de laine. Un &lt;emphasis&gt;éclat de laine&lt;/emphasis&gt; brille, au revers. Comme sur le métal ! Tu le vois, toi ? Oui, sur ce bord. Mila tourne la chaussette, lente. Elle écoute le radiateur, un instant. Psss. Le pied glisse, sans forcer. Elle est dedans. Et l'autre ? La deuxième suit, sans se presser. Les orteils sont au chaud ? Oui, papa. Mila s'assoit près du radiateur. Le métal chante, petit. Tu veux le livre du canard ? Oui, papa. Papa ouvre le livre. La couverture est lisse. Les pieds touchent le tapis libre.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1832,7 +1871,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1840,22 +1879,26 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
+          <t>-2st</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>low-pitch</t>
+        </is>
+      </c>
       <c r="AF5" s="2" t="inlineStr">
         <is>
           <t>medium</t>
@@ -1864,28 +1907,32 @@
       <c r="AG5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>éclat de laine</t>
+        </is>
+      </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>380</v>
+        <v>300</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>tense</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1894,40 +1941,63 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
       </c>
       <c r="AT5" s="2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AU5" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=obstacle; intention=alerter_sans_effrayer; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=elle_refuse_de_foncer_retrouve_l_eclat; tempo=resserré; sourire=aucun; respiration=retenue</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman tend les chaussettes.
-narrateur|Mila enfile la première.
-narrateur|Puis la deuxième.
-enfant-f|Elles sont douces.
-papa|Les orteils sont au chaud.
+          <t>maman|On enfile les chaussettes ?
+narrateur|Maman tend la première.
+narrateur|Mila pousse le pied, trop vite.
+narrateur|La laine se plie, de travers.
+enfant-f|Elle ne veut pas !
+narrateur|Mila veut foncer, d'un coup.
+narrateur|Mila refuse de foncer.
+narrateur|Ses épaules se serrent un peu.
+narrateur|Ça tape, dans sa poitrine.
+narrateur|Personne ne dit la suite.
+narrateur|Elle regarde le bord de laine.
+narrateur|Un éclat de laine brille, au revers.
+enfant-f|Comme sur le métal !
+papa|Tu le vois, toi ?
+enfant-f|Oui, sur ce bord.
+narrateur|Mila tourne la chaussette, lente.
+narrateur|Elle écoute le radiateur, un instant.
+narrateur|Psss.
+narrateur|Le pied glisse, sans forcer.
+enfant-f|Elle est dedans.
+maman|Et l'autre ?
+narrateur|La deuxième suit, sans se presser.
+papa|Les orteils sont au chaud ?
+enfant-f|Oui, papa.
 narrateur|Mila s'assoit près du radiateur.
-narrateur|Le métal chante tout bas.
-maman|On reste un moment ?
-enfant-f|Oui, maman.
-narrateur|Ses pieds touchent le tapis libre.
-narrateur|La laine est épaisse, un peu lourde.
+narrateur|Le métal chante, petit.
 papa|Tu veux le livre du canard ?
 enfant-f|Oui, papa.
 narrateur|Papa ouvre le livre.
 narrateur|La couverture est lisse.
-narrateur|Mila pose un pied sur l'autre.
-narrateur|Les chaussettes restent bien chaudes.</t>
+narrateur|Les pieds touchent le tapis libre.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>chaussettes,livre</t>
         </is>
       </c>
     </row>
@@ -1954,17 +2024,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Mes pieds sont au chaud. La laine a été retrouvée. Bravo, tu les as trouvées. Le radiateur chante encore. La laine reste douce sur les orteils.</t>
+          <t>Ils restent près du campement du radiateur. La chaleur touche les orteils de Mila. Mes pieds sont au chaud. Oui, la laine est là. Un coin de laine porte une trace claire. Comme l'éclat de laine, papa ! Tu le vois, toi ? Oui, sur mon orteil. Mila glisse un pied sur l'autre. La laine repose, un peu lourde. On le sent, maman. Tu le sens sur tes orteils ? Oui, il est chaud. Le livre du canard reste ouvert. L'éclat de laine tient sur l'orteil.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Mes pieds sont au chaud. La laine a été retrouvée. Bravo, tu les as trouvées. Le radiateur chante encore. La laine reste douce sur les orteils.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils restent près du campement du radiateur. La chaleur touche les orteils de Mila. Mes pieds sont au chaud. Oui, la laine est là. Un coin de laine porte une trace claire. Comme l'&lt;emphasis level="moderate"&gt;éclat de laine&lt;/emphasis&gt;, papa ! Tu le vois, toi ? Oui, sur mon orteil. Mila glisse un pied sur l'autre. La laine repose, un peu lourde. On le sent, maman. Tu le sens sur tes orteils ? Oui, il est chaud. Le livre du canard reste ouvert. L'éclat de laine tient sur l'orteil.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils restent près du campement du radiateur. La chaleur touche les orteils de Mila. Mes pieds sont au chaud. Oui, la laine est là. Un coin de laine porte une trace claire. Comme l'&lt;emphasis&gt;éclat de laine&lt;/emphasis&gt;, papa ! Tu le vois, toi ? Oui, sur mon orteil. Mila glisse un pied sur l'autre. La laine repose, un peu lourde. On le sent, maman. Tu le sens sur tes orteils ? Oui, il est chaud. Le livre du canard reste ouvert. L'éclat de laine tient sur l'orteil.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2011,18 +2081,18 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2031,12 +2101,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2045,17 +2115,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de laine</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2064,11 +2138,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2077,28 +2151,47 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse et fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_du_debut_tient_sur_l_orteil; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|Mes pieds sont au chaud.
-maman|La laine a été retrouvée.
-papa|Bravo, tu les as trouvées.
-narrateur|Le radiateur chante encore.
-narrateur|La laine reste douce sur les orteils.</t>
+          <t>narrateur|Ils restent près du campement du radiateur.
+narrateur|La chaleur touche les orteils de Mila.
+enfant-f|Mes pieds sont au chaud.
+maman|Oui, la laine est là.
+narrateur|Un coin de laine porte une trace claire.
+enfant-f|Comme l'éclat de laine, papa !
+papa|Tu le vois, toi ?
+enfant-f|Oui, sur mon orteil.
+narrateur|Mila glisse un pied sur l'autre.
+narrateur|La laine repose, un peu lourde.
+enfant-f|On le sent, maman.
+maman|Tu le sens sur tes orteils ?
+enfant-f|Oui, il est chaud.
+narrateur|Le livre du canard reste ouvert.
+narrateur|L'éclat de laine tient sur l'orteil.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>radiateur,laine</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2211,6 +2304,13 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
